--- a/temp.xlsx
+++ b/temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ramaakbar/Desktop/email-blast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860AFB56-EC42-2249-B3C6-B3C708E5F912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62D7A52-66D8-2447-BA4F-1015A618D798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>email</t>
   </si>
@@ -31,28 +31,13 @@
     <t>file</t>
   </si>
   <si>
-    <t>rmakbr26@gmail.com</t>
-  </si>
-  <si>
     <t>test.pdf</t>
-  </si>
-  <si>
-    <t>test2.pdf</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>ramaakbary@gmail.com</t>
-  </si>
-  <si>
-    <t>Wahyuning Suci Prabandini</t>
-  </si>
-  <si>
-    <t>suciprabandini2@gmail.com</t>
-  </si>
-  <si>
-    <t>rmakbr26@gmail.c</t>
+    <t>nohik31211@keevle.com</t>
   </si>
 </sst>
 </file>
@@ -434,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
@@ -444,7 +429,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -459,52 +444,154 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{91398FFE-236B-8040-BA7E-7C072BC24DBB}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{FCDF3576-F280-4942-97A2-1BCDF10C2391}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{B561848F-39D1-804B-9054-8B6BAD4E9EFB}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{C390917E-BFBD-E448-A87B-5E88104D32D6}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
